--- a/outputs/public/tables/keyness_condensed_results_table_JMIR_updated_SJ.xlsx
+++ b/outputs/public/tables/keyness_condensed_results_table_JMIR_updated_SJ.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sayegh-jodehl/Documents/Publikationen/Korpusanalyse_JMIR/Manuelle Codierung/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31B2766D-966A-0A47-AEB5-41A5F23AE779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="680" windowWidth="24500" windowHeight="18960" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4280" yWindow="680" windowWidth="24500" windowHeight="18960" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="JMIR_table" sheetId="1" r:id="rId1"/>
-    <sheet name="Category_counts" sheetId="2" r:id="rId2"/>
-    <sheet name="Representative_items" sheetId="3" r:id="rId3"/>
-    <sheet name="Coding_QA" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="JMIR_table" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Category_counts" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Representative_items" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Coding_QA" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="216">
   <si>
     <t>Result domain</t>
   </si>
@@ -205,409 +199,456 @@
     <t>This domain included documentation logistics and room/resource coordination; after contextual review, ‘Raum’ was coded here rather than as therapy/group content.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Manual category</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Direction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Accepted items, n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Core result, n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Supporting result, n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Other accepted role, n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>direct</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>Interaction/politeness</t>
+  </si>
+  <si>
+    <t>Colleague reference/addressivity</t>
+  </si>
+  <si>
+    <t>Technical/platform-related</t>
+  </si>
+  <si>
+    <t>General discourse marker</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>View</t>
+  </si>
+  <si>
+    <t>Item type</t>
+  </si>
+  <si>
     <t>Manual category</t>
   </si>
   <si>
-    <t>Direction</t>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Log likelihood</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Interpretation note</t>
+  </si>
+  <si>
+    <t>PatName</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>token</t>
+  </si>
+  <si>
+    <t>Core result</t>
+  </si>
+  <si>
+    <t>content_tokens_direct</t>
+  </si>
+  <si>
+    <t>KolName PatName</t>
+  </si>
+  <si>
+    <t>bigram</t>
+  </si>
+  <si>
+    <t>content_bigrams_direct</t>
+  </si>
+  <si>
+    <t>Composite bigram combining colleague and patient reference; coded primarily as patient reference because the patient appears to be the informational anchor, with colleague addressivity as secondary function.”</t>
+  </si>
+  <si>
+    <t>PatName bekommt</t>
+  </si>
+  <si>
+    <t>PatName QuestionMark</t>
+  </si>
+  <si>
+    <t>interaction</t>
+  </si>
+  <si>
+    <t>interaction_bigrams_direct</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName Atorvastatin</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName OGTT Rö</t>
+  </si>
+  <si>
+    <t>trigram</t>
+  </si>
+  <si>
+    <t>content_trigrams_direct</t>
+  </si>
+  <si>
+    <t>PatName PatName</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName OGTT</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName</t>
+  </si>
+  <si>
+    <t>interaction_tokens_group</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName kein_Todo</t>
+  </si>
+  <si>
+    <t>content_bigrams_group</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName Hashtag_PatName</t>
+  </si>
+  <si>
+    <t>interaction_bigrams_group</t>
+  </si>
+  <si>
+    <t>kein_Todo Hashtag_PatName</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName Hashtag_PatName Hashtag_PatName</t>
+  </si>
+  <si>
+    <t>interaction_trigrams_group</t>
+  </si>
+  <si>
+    <t>Mention_KolName Hashtag_PatName</t>
+  </si>
+  <si>
+    <t>WE Hashtag_PatName</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName kein</t>
+  </si>
+  <si>
+    <t>fertig</t>
+  </si>
+  <si>
+    <t>interaction_tokens_direct</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName Atorvastatin neu</t>
+  </si>
+  <si>
+    <t>interaction_trigrams_direct</t>
+  </si>
+  <si>
+    <t>angefangen Muskelschmerzen evaluieren</t>
+  </si>
+  <si>
+    <t>evaluieren Suizidalität evaluieren</t>
+  </si>
+  <si>
+    <t>neu angefangen Muskelschmerzen</t>
+  </si>
+  <si>
+    <t>TSH bitte vidieren</t>
+  </si>
+  <si>
+    <t>Supporting result</t>
+  </si>
+  <si>
+    <t>erniedrigtem TSH bitte</t>
+  </si>
+  <si>
+    <t>hab</t>
+  </si>
+  <si>
+    <t>kein_Todo</t>
+  </si>
+  <si>
+    <t>Hashtag_PatName kein_Todo Hashtag_PatName</t>
+  </si>
+  <si>
+    <t>kein_Todo Hashtag_PatName kein_Todo</t>
+  </si>
+  <si>
+    <t>aktives Todo</t>
+  </si>
+  <si>
+    <t>anwesend</t>
+  </si>
+  <si>
+    <t>Gruppe</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>Musiktherapie</t>
+  </si>
+  <si>
+    <t>MT Gruppe</t>
+  </si>
+  <si>
+    <t>Rückmeldung MT</t>
+  </si>
+  <si>
+    <t>Rückmeldung MT Gruppe</t>
+  </si>
+  <si>
+    <t>Gruppe anwesend</t>
+  </si>
+  <si>
+    <t>KT Gruppe</t>
+  </si>
+  <si>
+    <t>morgen</t>
+  </si>
+  <si>
+    <t>uhr</t>
+  </si>
+  <si>
+    <t>10 Uhr</t>
+  </si>
+  <si>
+    <t>12 30</t>
+  </si>
+  <si>
+    <t>11 30</t>
+  </si>
+  <si>
+    <t>morgen früh</t>
+  </si>
+  <si>
+    <t>um 13 Uhr</t>
+  </si>
+  <si>
+    <t>12 00 Uhr</t>
+  </si>
+  <si>
+    <t>Datum</t>
+  </si>
+  <si>
+    <t>20 00</t>
+  </si>
+  <si>
+    <t>13 30 20</t>
+  </si>
+  <si>
+    <t>content_trigrams_group</t>
+  </si>
+  <si>
+    <t>Datum / E</t>
+  </si>
+  <si>
+    <t>WE</t>
+  </si>
+  <si>
+    <t>Wochenende</t>
+  </si>
+  <si>
+    <t>Z n</t>
+  </si>
+  <si>
+    <t>Abkürzung für zur Nacht</t>
+  </si>
+  <si>
+    <t>Atorvastatin neu angefangen</t>
+  </si>
+  <si>
+    <t>Muskelschmerzen evaluieren Suizidalität</t>
+  </si>
+  <si>
+    <t>Keratosen umsetzen KolName</t>
+  </si>
+  <si>
+    <t>Seb Keratosen umsetzen</t>
+  </si>
+  <si>
+    <t>30 20 00</t>
+  </si>
+  <si>
+    <t>00 20 00</t>
+  </si>
+  <si>
+    <t>12 00 20</t>
+  </si>
+  <si>
+    <t>KolName ÖGD</t>
+  </si>
+  <si>
+    <t>KolName Kolo</t>
+  </si>
+  <si>
+    <t>koloskopie</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Blutentnahme</t>
+  </si>
+  <si>
+    <t>Kalinor</t>
+  </si>
+  <si>
+    <t>Guten Morgen</t>
+  </si>
+  <si>
+    <t>KolName will Dermakonsil</t>
+  </si>
+  <si>
+    <t>QuestionMark</t>
+  </si>
+  <si>
+    <t>KolName</t>
+  </si>
+  <si>
+    <t>ja</t>
+  </si>
+  <si>
+    <t>Hallo KolName</t>
+  </si>
+  <si>
+    <t>Hi</t>
+  </si>
+  <si>
+    <t>Hi KolName</t>
+  </si>
+  <si>
+    <t>Mention_KolName</t>
+  </si>
+  <si>
+    <t>Mention_KolName Mention_KolName</t>
+  </si>
+  <si>
+    <t>Mention_KolName Liebe KolName</t>
+  </si>
+  <si>
+    <t>Mention_KolName Mention_KolName Mention_KolName</t>
+  </si>
+  <si>
+    <t>KolName ÖGD KolName</t>
+  </si>
+  <si>
+    <t>KolName Kolo KolName</t>
+  </si>
+  <si>
+    <t>Mention_All</t>
+  </si>
+  <si>
+    <t>Good Morning Klinik</t>
+  </si>
+  <si>
+    <t>Brief</t>
+  </si>
+  <si>
+    <t>Fach</t>
+  </si>
+  <si>
+    <t>Teil</t>
+  </si>
+  <si>
+    <t>zum Teil …erledigt</t>
+  </si>
+  <si>
+    <t>schreiben</t>
+  </si>
+  <si>
+    <t>fehlt</t>
+  </si>
+  <si>
+    <t>Raum</t>
+  </si>
+  <si>
+    <t>Contextual review of trigrams showed that Raum refers to room/resource coordination between colleagues, not to therapy/group context.</t>
+  </si>
+  <si>
+    <t>Raum KolName</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Source file</t>
+  </si>
+  <si>
+    <t>keyness_review_top_items_coding_SJ.xlsx</t>
+  </si>
+  <si>
+    <t>Generated</t>
+  </si>
+  <si>
+    <t>2026-06-19 20:34</t>
   </si>
   <si>
     <t>Accepted items, n</t>
-  </si>
-  <si>
-    <t>Core result, n</t>
-  </si>
-  <si>
-    <t>Supporting result, n</t>
-  </si>
-  <si>
-    <t>Other accepted role, n</t>
-  </si>
-  <si>
-    <t>direct</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>Interaction/politeness</t>
-  </si>
-  <si>
-    <t>Colleague reference/addressivity</t>
-  </si>
-  <si>
-    <t>Technical/platform-related</t>
-  </si>
-  <si>
-    <t>General discourse marker</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>View</t>
-  </si>
-  <si>
-    <t>Item type</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Log likelihood</t>
-  </si>
-  <si>
-    <t>Sheet</t>
-  </si>
-  <si>
-    <t>Interpretation note</t>
-  </si>
-  <si>
-    <t>PatName</t>
-  </si>
-  <si>
-    <t>content</t>
-  </si>
-  <si>
-    <t>token</t>
-  </si>
-  <si>
-    <t>Core result</t>
-  </si>
-  <si>
-    <t>content_tokens_direct</t>
-  </si>
-  <si>
-    <t>KolName PatName</t>
-  </si>
-  <si>
-    <t>bigram</t>
-  </si>
-  <si>
-    <t>content_bigrams_direct</t>
-  </si>
-  <si>
-    <t>Composite bigram combining colleague and patient reference; coded primarily as patient reference because the patient appears to be the informational anchor, with colleague addressivity as secondary function.”</t>
-  </si>
-  <si>
-    <t>PatName bekommt</t>
-  </si>
-  <si>
-    <t>PatName QuestionMark</t>
-  </si>
-  <si>
-    <t>interaction</t>
-  </si>
-  <si>
-    <t>interaction_bigrams_direct</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName Atorvastatin</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName OGTT Rö</t>
-  </si>
-  <si>
-    <t>trigram</t>
-  </si>
-  <si>
-    <t>content_trigrams_direct</t>
-  </si>
-  <si>
-    <t>PatName PatName</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName OGTT</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName</t>
-  </si>
-  <si>
-    <t>interaction_tokens_group</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName kein_Todo</t>
-  </si>
-  <si>
-    <t>content_bigrams_group</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName Hashtag_PatName</t>
-  </si>
-  <si>
-    <t>interaction_bigrams_group</t>
-  </si>
-  <si>
-    <t>kein_Todo Hashtag_PatName</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName Hashtag_PatName Hashtag_PatName</t>
-  </si>
-  <si>
-    <t>interaction_trigrams_group</t>
-  </si>
-  <si>
-    <t>Mention_KolName Hashtag_PatName</t>
-  </si>
-  <si>
-    <t>WE Hashtag_PatName</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName kein</t>
-  </si>
-  <si>
-    <t>fertig</t>
-  </si>
-  <si>
-    <t>interaction_tokens_direct</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName Atorvastatin neu</t>
-  </si>
-  <si>
-    <t>interaction_trigrams_direct</t>
-  </si>
-  <si>
-    <t>angefangen Muskelschmerzen evaluieren</t>
-  </si>
-  <si>
-    <t>evaluieren Suizidalität evaluieren</t>
-  </si>
-  <si>
-    <t>neu angefangen Muskelschmerzen</t>
-  </si>
-  <si>
-    <t>TSH bitte vidieren</t>
-  </si>
-  <si>
-    <t>Supporting result</t>
-  </si>
-  <si>
-    <t>erniedrigtem TSH bitte</t>
-  </si>
-  <si>
-    <t>hab</t>
-  </si>
-  <si>
-    <t>kein_Todo</t>
-  </si>
-  <si>
-    <t>Hashtag_PatName kein_Todo Hashtag_PatName</t>
-  </si>
-  <si>
-    <t>kein_Todo Hashtag_PatName kein_Todo</t>
-  </si>
-  <si>
-    <t>aktives Todo</t>
-  </si>
-  <si>
-    <t>anwesend</t>
-  </si>
-  <si>
-    <t>Gruppe</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>Musiktherapie</t>
-  </si>
-  <si>
-    <t>MT Gruppe</t>
-  </si>
-  <si>
-    <t>Rückmeldung MT</t>
-  </si>
-  <si>
-    <t>Rückmeldung MT Gruppe</t>
-  </si>
-  <si>
-    <t>Gruppe anwesend</t>
-  </si>
-  <si>
-    <t>KT Gruppe</t>
-  </si>
-  <si>
-    <t>morgen</t>
-  </si>
-  <si>
-    <t>uhr</t>
-  </si>
-  <si>
-    <t>10 Uhr</t>
-  </si>
-  <si>
-    <t>12 30</t>
-  </si>
-  <si>
-    <t>11 30</t>
-  </si>
-  <si>
-    <t>morgen früh</t>
-  </si>
-  <si>
-    <t>um 13 Uhr</t>
-  </si>
-  <si>
-    <t>12 00 Uhr</t>
-  </si>
-  <si>
-    <t>Datum</t>
-  </si>
-  <si>
-    <t>20 00</t>
-  </si>
-  <si>
-    <t>13 30 20</t>
-  </si>
-  <si>
-    <t>content_trigrams_group</t>
-  </si>
-  <si>
-    <t>Datum / E</t>
-  </si>
-  <si>
-    <t>WE</t>
-  </si>
-  <si>
-    <t>Wochenende</t>
-  </si>
-  <si>
-    <t>Z n</t>
-  </si>
-  <si>
-    <t>Abkürzung für zur Nacht</t>
-  </si>
-  <si>
-    <t>Atorvastatin neu angefangen</t>
-  </si>
-  <si>
-    <t>Muskelschmerzen evaluieren Suizidalität</t>
-  </si>
-  <si>
-    <t>Keratosen umsetzen KolName</t>
-  </si>
-  <si>
-    <t>Seb Keratosen umsetzen</t>
-  </si>
-  <si>
-    <t>30 20 00</t>
-  </si>
-  <si>
-    <t>00 20 00</t>
-  </si>
-  <si>
-    <t>12 00 20</t>
-  </si>
-  <si>
-    <t>KolName ÖGD</t>
-  </si>
-  <si>
-    <t>KolName Kolo</t>
-  </si>
-  <si>
-    <t>koloskopie</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>Blutentnahme</t>
-  </si>
-  <si>
-    <t>Kalinor</t>
-  </si>
-  <si>
-    <t>Guten Morgen</t>
-  </si>
-  <si>
-    <t>KolName will Dermakonsil</t>
-  </si>
-  <si>
-    <t>QuestionMark</t>
-  </si>
-  <si>
-    <t>KolName</t>
-  </si>
-  <si>
-    <t>ja</t>
-  </si>
-  <si>
-    <t>Hallo KolName</t>
-  </si>
-  <si>
-    <t>Hi</t>
-  </si>
-  <si>
-    <t>Hi KolName</t>
-  </si>
-  <si>
-    <t>Mention_KolName</t>
-  </si>
-  <si>
-    <t>Mention_KolName Mention_KolName</t>
-  </si>
-  <si>
-    <t>Mention_KolName Liebe KolName</t>
-  </si>
-  <si>
-    <t>Mention_KolName Mention_KolName Mention_KolName</t>
-  </si>
-  <si>
-    <t>KolName ÖGD KolName</t>
-  </si>
-  <si>
-    <t>KolName Kolo KolName</t>
-  </si>
-  <si>
-    <t>Mention_All</t>
-  </si>
-  <si>
-    <t>Good Morning Klinik</t>
-  </si>
-  <si>
-    <t>Brief</t>
-  </si>
-  <si>
-    <t>Fach</t>
-  </si>
-  <si>
-    <t>Teil</t>
-  </si>
-  <si>
-    <t>zum Teil …erledigt</t>
-  </si>
-  <si>
-    <t>schreiben</t>
-  </si>
-  <si>
-    <t>fehlt</t>
-  </si>
-  <si>
-    <t>Raum</t>
-  </si>
-  <si>
-    <t>Contextual review of trigrams showed that Raum refers to room/resource coordination between colleagues, not to therapy/group context.</t>
-  </si>
-  <si>
-    <t>Raum KolName</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Source file</t>
-  </si>
-  <si>
-    <t>keyness_review_top_items_coding_SJ.xlsx</t>
-  </si>
-  <si>
-    <t>Generated</t>
-  </si>
-  <si>
-    <t>2026-06-19 20:34</t>
   </si>
   <si>
     <t>Excluded items, n</t>
@@ -664,25 +705,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
@@ -714,25 +761,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -748,64 +794,104 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JMIRCondensedTable" displayName="JMIRCondensedTable" ref="A1:H8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="JMIRCondensedTable" displayName="JMIRCondensedTable" ref="A1:H8" totalsRowShown="1" headerRowCount="0">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Result domain"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Included manual categories"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Dominant modality"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Direct accepted/core, n"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Group accepted/core, n"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Representative direct key items"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Representative group key items"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Interpretation for manuscript"/>
+    <tableColumn id="1" name="Result domain"/>
+    <tableColumn id="2" name="Included manual categories"/>
+    <tableColumn id="3" name="Dominant modality"/>
+    <tableColumn id="4" name="Direct accepted/core, n"/>
+    <tableColumn id="5" name="Group accepted/core, n"/>
+    <tableColumn id="6" name="Representative direct key items"/>
+    <tableColumn id="7" name="Representative group key items"/>
+    <tableColumn id="8" name="Interpretation for manuscript"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CategoryCountsTable" displayName="CategoryCountsTable" ref="A1:F21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="CategoryCountsTable" displayName="CategoryCountsTable" ref="A1:F21" totalsRowShown="1" headerRowCount="0">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Manual category"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Direction"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Accepted items, n"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Core result, n"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Supporting result, n"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Other accepted role, n"/>
+    <tableColumn id="1" name="Manual category"/>
+    <tableColumn id="2" name="Direction"/>
+    <tableColumn id="3" name="Accepted items, n"/>
+    <tableColumn id="4" name="Core result, n"/>
+    <tableColumn id="5" name="Supporting result, n"/>
+    <tableColumn id="6" name="Other accepted role, n"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="RepresentativeItemsTable" displayName="RepresentativeItemsTable" ref="A1:J96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" name="RepresentativeItemsTable" displayName="RepresentativeItemsTable" ref="A1:J96" totalsRowShown="1" headerRowCount="0">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Result domain"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Direction"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Item"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="View"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Item type"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Manual category"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Role"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Log likelihood"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Sheet"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Interpretation note"/>
+    <tableColumn id="1" name="Result domain"/>
+    <tableColumn id="2" name="Direction"/>
+    <tableColumn id="3" name="Item"/>
+    <tableColumn id="4" name="View"/>
+    <tableColumn id="5" name="Item type"/>
+    <tableColumn id="6" name="Manual category"/>
+    <tableColumn id="7" name="Role"/>
+    <tableColumn id="8" name="Log likelihood"/>
+    <tableColumn id="9" name="Sheet"/>
+    <tableColumn id="10" name="Interpretation note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="CodingCorrectionsTable" displayName="CodingCorrectionsTable" ref="A13:H17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" name="CodingCorrectionsTable" displayName="CodingCorrectionsTable" ref="A13:H17" totalsRowShown="1" headerRowCount="0">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Sheet"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Row"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Item"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Previous category"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Updated category"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Previous status"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Updated status"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Rationale"/>
+    <tableColumn id="1" name="Sheet"/>
+    <tableColumn id="2" name="Row"/>
+    <tableColumn id="3" name="Item"/>
+    <tableColumn id="4" name="Previous category"/>
+    <tableColumn id="5" name="Updated category"/>
+    <tableColumn id="6" name="Previous status"/>
+    <tableColumn id="7" name="Updated status"/>
+    <tableColumn id="8" name="Rationale"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -959,9 +1045,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="32" customWidth="1"/>
     <col min="3" max="5" width="16" customWidth="1"/>
@@ -969,7 +1055,7 @@
     <col min="8" max="8" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="45.25" customHeight="1">
+    <row r="1" ht="45.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -995,7 +1081,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="82.75" customHeight="1">
+    <row r="2" ht="82.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1021,7 +1107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="82.75" customHeight="1">
+    <row r="3" ht="82.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1047,7 +1133,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="82.75" customHeight="1">
+    <row r="4" ht="82.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -1073,7 +1159,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="82.75" customHeight="1">
+    <row r="5" ht="82.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1099,7 +1185,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="82.75" customHeight="1">
+    <row r="6" ht="82.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -1125,7 +1211,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="82.75" customHeight="1">
+    <row r="7" ht="82.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
@@ -1151,7 +1237,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="82.75" customHeight="1">
+    <row r="8" ht="82.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>53</v>
       </c>
@@ -1186,9 +1272,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1198,7 +1284,7 @@
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32">
+    <row r="1" ht="32" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1217,13 +1303,25 @@
       <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15">
+      <c r="G1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2">
         <v>14</v>
@@ -1237,13 +1335,17 @@
       <c r="F2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2">
         <v>17</v>
@@ -1257,13 +1359,17 @@
       <c r="F3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="2">
         <v>13</v>
@@ -1277,13 +1383,17 @@
       <c r="F4" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2">
         <v>50</v>
@@ -1297,13 +1407,17 @@
       <c r="F5" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1317,13 +1431,17 @@
       <c r="F6" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="2">
         <v>59</v>
@@ -1337,13 +1455,17 @@
       <c r="F7" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2">
         <v>20</v>
@@ -1357,13 +1479,17 @@
       <c r="F8" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" s="2">
         <v>8</v>
@@ -1377,13 +1503,17 @@
       <c r="F9" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15">
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="2">
         <v>39</v>
@@ -1397,13 +1527,17 @@
       <c r="F10" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2">
         <v>18</v>
@@ -1417,13 +1551,17 @@
       <c r="F11" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15">
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="2">
         <v>47</v>
@@ -1437,13 +1575,17 @@
       <c r="F12" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15">
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -1457,13 +1599,17 @@
       <c r="F13" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15">
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2">
         <v>19</v>
@@ -1477,13 +1623,17 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15">
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2">
         <v>13</v>
@@ -1497,13 +1647,17 @@
       <c r="F15" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="15">
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" s="2">
         <v>7</v>
@@ -1517,13 +1671,17 @@
       <c r="F16" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="2">
         <v>4</v>
@@ -1537,13 +1695,17 @@
       <c r="F17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15">
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -1557,13 +1719,17 @@
       <c r="F18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15">
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
@@ -1577,13 +1743,17 @@
       <c r="F19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -1597,13 +1767,17 @@
       <c r="F20" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -1617,6 +1791,10 @@
       <c r="F21" s="2">
         <v>0</v>
       </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1627,9 +1805,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J96"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1642,2805 +1820,2805 @@
     <col min="10" max="10" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16">
+    <row r="1" ht="16" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="2">
-        <v>320.04698068527921</v>
+        <v>320.0469806852792</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="60">
+    <row r="3" ht="60" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H3" s="2">
         <v>51.13233211372485</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H4" s="2">
-        <v>25.566166056862421</v>
+        <v>25.56616605686242</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="15">
+    <row r="5" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H5" s="2">
-        <v>24.395715631100138</v>
+        <v>24.39571563110014</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="15">
+    <row r="6" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H6" s="2">
-        <v>23.599537898642239</v>
+        <v>23.59953789864224</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="15">
+    <row r="7" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H7" s="2">
-        <v>23.412580529340641</v>
+        <v>23.41258052934064</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="15">
+    <row r="8" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2">
         <v>22.40369947087321</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="15">
+    <row r="9" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H9" s="2">
-        <v>19.666281582201869</v>
+        <v>19.66628158220187</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="15">
+    <row r="10" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H10" s="2">
         <v>1464.277237266906</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="15">
+    <row r="11" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H11" s="2">
-        <v>441.01469105893068</v>
+        <v>441.0146910589307</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="30">
+    <row r="12" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H12" s="2">
-        <v>354.57892884703227</v>
+        <v>354.5789288470323</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="15">
+    <row r="13" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H13" s="2">
-        <v>246.84448733697411</v>
+        <v>246.8444873369741</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="45">
+    <row r="14" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H14" s="2">
-        <v>164.78315153084441</v>
+        <v>164.7831515308444</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="30">
+    <row r="15" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H15" s="2">
-        <v>61.286271202557543</v>
+        <v>61.28627120255754</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="15">
+    <row r="16" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H16" s="2">
-        <v>51.536726107866862</v>
+        <v>51.53672610786686</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:10" ht="15">
+    <row r="17" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H17" s="2">
-        <v>46.851569188969869</v>
+        <v>46.85156918896987</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" ht="15">
+    <row r="18" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2">
-        <v>58.999757341478613</v>
+        <v>58.99975734147861</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10" ht="15">
+    <row r="19" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H19" s="2">
-        <v>23.802514670720068</v>
+        <v>23.80251467072007</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:10" ht="30">
+    <row r="20" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H20" s="2">
-        <v>23.802514670720068</v>
+        <v>23.80251467072007</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" ht="15">
+    <row r="21" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H21" s="2">
-        <v>23.802514670720068</v>
+        <v>23.80251467072007</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" ht="15">
+    <row r="22" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H22" s="2">
-        <v>23.802514670720068</v>
+        <v>23.80251467072007</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:10" ht="15">
+    <row r="23" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H23" s="2">
-        <v>23.802514670720068</v>
+        <v>23.80251467072007</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10" ht="15">
+    <row r="24" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H24" s="2">
-        <v>23.802514670720068</v>
+        <v>23.80251467072007</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:10" ht="15">
+    <row r="25" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2">
-        <v>70.326047939568383</v>
+        <v>70.32604793956838</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:10" ht="15">
+    <row r="26" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H26" s="2">
-        <v>717.71315316215953</v>
+        <v>717.7131531621595</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J26" s="2"/>
     </row>
-    <row r="27" spans="1:10" ht="15">
+    <row r="27" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H27" s="2">
-        <v>526.28339394129466</v>
+        <v>526.2833939412947</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="1:10" ht="15">
+    <row r="28" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H28" s="2">
-        <v>295.69004016388271</v>
+        <v>295.6900401638827</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="1:10" ht="30">
+    <row r="29" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H29" s="2">
-        <v>208.50200431646331</v>
+        <v>208.5020043164633</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="1:10" ht="30">
+    <row r="30" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H30" s="2">
         <v>162.2578270850091</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="1:10" ht="15">
+    <row r="31" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H31" s="2">
-        <v>60.191873502511882</v>
+        <v>60.19187350251188</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J31" s="2"/>
     </row>
-    <row r="32" spans="1:10" ht="15">
+    <row r="32" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H32" s="2">
-        <v>54.719885002283519</v>
+        <v>54.71988500228352</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="1:10" ht="15">
+    <row r="33" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H33" s="2">
-        <v>52.531089602192189</v>
+        <v>52.53108960219219</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J33" s="2"/>
     </row>
-    <row r="34" spans="1:10" ht="30">
+    <row r="34" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2">
-        <v>21.632909740422051</v>
+        <v>21.63290974042205</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J34" s="2"/>
     </row>
-    <row r="35" spans="1:10" ht="30">
+    <row r="35" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H35" s="2">
-        <v>182.11232975117341</v>
+        <v>182.1123297511734</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J35" s="2"/>
     </row>
-    <row r="36" spans="1:10" ht="30">
+    <row r="36" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H36" s="2">
         <v>155.0275462777623</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J36" s="2"/>
     </row>
-    <row r="37" spans="1:10" ht="30">
+    <row r="37" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H37" s="2">
         <v>119.8591304436855</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="30">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H38" s="2">
-        <v>88.646213703699303</v>
+        <v>88.6462137036993</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J38" s="2"/>
     </row>
-    <row r="39" spans="1:10" ht="30">
+    <row r="39" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H39" s="2">
-        <v>74.419043603105592</v>
+        <v>74.41904360310559</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="1:10" ht="30">
+    <row r="40" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H40" s="2">
-        <v>63.035364622965297</v>
+        <v>63.0353646229653</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J40" s="2"/>
     </row>
-    <row r="41" spans="1:10" ht="30">
+    <row r="41" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H41" s="2">
-        <v>54.719885002283519</v>
+        <v>54.71988500228352</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J41" s="2"/>
     </row>
-    <row r="42" spans="1:10" ht="30">
+    <row r="42" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H42" s="2">
-        <v>41.587112601735477</v>
+        <v>41.58711260173548</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J42" s="2"/>
     </row>
-    <row r="43" spans="1:10" ht="15">
+    <row r="43" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H43" s="2">
-        <v>85.013533211715469</v>
+        <v>85.01353321171547</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J43" s="2"/>
     </row>
-    <row r="44" spans="1:10" ht="15">
+    <row r="44" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H44" s="2">
-        <v>33.023823627907021</v>
+        <v>33.02382362790702</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J44" s="2"/>
     </row>
-    <row r="45" spans="1:10" ht="15">
+    <row r="45" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H45" s="2">
-        <v>31.466050531522988</v>
+        <v>31.46605053152299</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J45" s="2"/>
     </row>
-    <row r="46" spans="1:10" ht="15">
+    <row r="46" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H46" s="2">
-        <v>25.566166056862421</v>
+        <v>25.56616605686242</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J46" s="2"/>
     </row>
-    <row r="47" spans="1:10" ht="15">
+    <row r="47" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H47" s="2">
-        <v>16.090313005454021</v>
+        <v>16.09031300545402</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J47" s="2"/>
     </row>
-    <row r="48" spans="1:10" ht="15">
+    <row r="48" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H48" s="2">
-        <v>15.198079125113059</v>
+        <v>15.19807912511306</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J48" s="2"/>
     </row>
-    <row r="49" spans="1:10" ht="15">
+    <row r="49" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H49" s="2">
         <v>10.0517082544992</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J49" s="2"/>
     </row>
-    <row r="50" spans="1:10" ht="15">
+    <row r="50" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H50" s="2">
-        <v>5.1199515174835399</v>
+        <v>5.11995151748354</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J50" s="2"/>
     </row>
-    <row r="51" spans="1:10" ht="15">
+    <row r="51" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H51" s="2">
         <v>110.3958490672793</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" spans="1:10" ht="15">
+    <row r="52" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H52" s="2">
-        <v>56.908680402374863</v>
+        <v>56.90868040237486</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" spans="1:10" ht="15">
+    <row r="53" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H53" s="2">
-        <v>19.308258303321519</v>
+        <v>19.30825830332152</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" spans="1:10" ht="15">
+    <row r="54" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H54" s="2">
         <v>10.39675447101928</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" spans="1:10" ht="15">
+    <row r="55" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2">
-        <v>111.93686268318559</v>
+        <v>111.9368626831856</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2">
-        <v>79.891032103333941</v>
+        <v>79.89103210333394</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="15">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H57" s="2">
         <v>28.09509663520878</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J57" s="2"/>
     </row>
-    <row r="58" spans="1:10" ht="15">
+    <row r="58" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H58" s="2">
         <v>28.09509663520878</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J58" s="2"/>
     </row>
-    <row r="59" spans="1:10" ht="30">
+    <row r="59" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H59" s="2">
         <v>28.09509663520878</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J59" s="2"/>
     </row>
-    <row r="60" spans="1:10" ht="30">
+    <row r="60" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H60" s="2">
         <v>28.09509663520878</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J60" s="2"/>
     </row>
-    <row r="61" spans="1:10" ht="15">
+    <row r="61" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H61" s="2">
         <v>28.09509663520878</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J61" s="2"/>
     </row>
-    <row r="62" spans="1:10" ht="15">
+    <row r="62" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H62" s="2">
         <v>28.09509663520878</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J62" s="2"/>
     </row>
-    <row r="63" spans="1:10" ht="15">
+    <row r="63" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H63" s="2">
         <v>25.75383858227471</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J63" s="2"/>
     </row>
-    <row r="64" spans="1:10" ht="15">
+    <row r="64" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H64" s="2">
         <v>25.75383858227471</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J64" s="2"/>
     </row>
-    <row r="65" spans="1:10" ht="15">
+    <row r="65" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H65" s="2">
-        <v>25.955738374162181</v>
+        <v>25.95573837416218</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J65" s="2"/>
     </row>
-    <row r="66" spans="1:10" ht="15">
+    <row r="66" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H66" s="2">
-        <v>24.101757061722019</v>
+        <v>24.10175706172202</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J66" s="2"/>
     </row>
-    <row r="67" spans="1:10" ht="15">
+    <row r="67" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H67" s="2">
         <v>14.83185049952125</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J67" s="2"/>
     </row>
-    <row r="68" spans="1:10" ht="15">
+    <row r="68" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H68" s="2">
         <v>14.83185049952125</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J68" s="2"/>
     </row>
-    <row r="69" spans="1:10" ht="15">
+    <row r="69" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H69" s="2">
         <v>26.23687874582313</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J69" s="2"/>
     </row>
-    <row r="70" spans="1:10" ht="15">
+    <row r="70" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H70" s="2">
-        <v>24.362815978264329</v>
+        <v>24.36281597826433</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="15">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2">
-        <v>66.326410461056469</v>
+        <v>66.32641046105647</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="15">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2">
-        <v>52.438369569112403</v>
+        <v>52.4383695691124</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J72" s="2"/>
     </row>
-    <row r="73" spans="1:10" ht="15">
+    <row r="73" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H73" s="2">
-        <v>49.033108066393382</v>
+        <v>49.03310806639338</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J73" s="2"/>
     </row>
-    <row r="74" spans="1:10" ht="15">
+    <row r="74" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H74" s="2">
         <v>25.75383858227471</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J74" s="2"/>
     </row>
-    <row r="75" spans="1:10" ht="15">
+    <row r="75" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H75" s="2">
-        <v>513.50997387688813</v>
+        <v>513.5099738768881</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J75" s="2"/>
     </row>
-    <row r="76" spans="1:10" ht="15">
+    <row r="76" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H76" s="2">
-        <v>280.87111226792081</v>
+        <v>280.8711122679208</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J76" s="2"/>
     </row>
-    <row r="77" spans="1:10" ht="15">
+    <row r="77" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H77" s="2">
         <v>200.2697511060947</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J77" s="2"/>
     </row>
-    <row r="78" spans="1:10" ht="15">
+    <row r="78" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H78" s="2">
-        <v>195.35984077816479</v>
+        <v>195.3598407781648</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J78" s="2"/>
     </row>
-    <row r="79" spans="1:10" ht="15">
+    <row r="79" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H79" s="2">
-        <v>159.39412824524339</v>
+        <v>159.3941282452434</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J79" s="2"/>
     </row>
-    <row r="80" spans="1:10" ht="15">
+    <row r="80" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H80" s="2">
         <v>157.3266315010367</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J80" s="2"/>
     </row>
-    <row r="81" spans="1:10" ht="15">
+    <row r="81" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H81" s="2">
-        <v>369.05573860597377</v>
+        <v>369.0557386059738</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J81" s="2"/>
     </row>
-    <row r="82" spans="1:10" ht="30">
+    <row r="82" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H82" s="2">
         <v>108.3453723045214</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J82" s="2"/>
     </row>
-    <row r="83" spans="1:10" ht="15">
+    <row r="83" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H83" s="2">
         <v>22.24777574928186</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J83" s="2"/>
     </row>
-    <row r="84" spans="1:10" ht="45">
+    <row r="84" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H84" s="2">
         <v>16.6858318119614</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J84" s="2"/>
     </row>
-    <row r="85" spans="1:10" ht="15">
+    <row r="85" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H85" s="2">
-        <v>15.758841155741321</v>
+        <v>15.75884115574132</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J85" s="2"/>
     </row>
-    <row r="86" spans="1:10" ht="15">
+    <row r="86" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H86" s="2">
-        <v>13.904859843301169</v>
+        <v>13.90485984330117</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J86" s="2"/>
     </row>
-    <row r="87" spans="1:10" ht="15">
+    <row r="87" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2">
-        <v>77.409021744880221</v>
+        <v>77.40902174488022</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J87" s="2"/>
     </row>
-    <row r="88" spans="1:10" ht="15">
+    <row r="88" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2">
-        <v>18.539813124401551</v>
+        <v>18.53981312440155</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J88" s="2"/>
     </row>
-    <row r="89" spans="1:10" ht="30">
+    <row r="89" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H89" s="2">
-        <v>67.877453882882094</v>
+        <v>67.8774538828821</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J89" s="2"/>
     </row>
-    <row r="90" spans="1:10" ht="30">
+    <row r="90" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H90" s="2">
         <v>105.7550219848484</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J90" s="2"/>
     </row>
-    <row r="91" spans="1:10" ht="30">
+    <row r="91" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2">
-        <v>50.630312233184803</v>
+        <v>50.6303122331848</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J91" s="2"/>
     </row>
-    <row r="92" spans="1:10" ht="30">
+    <row r="92" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2">
-        <v>47.141393951280463</v>
+        <v>47.14139395128046</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="30">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2">
-        <v>44.017995483326629</v>
+        <v>44.01799548332663</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J93" s="2"/>
     </row>
-    <row r="94" spans="1:10" ht="30">
+    <row r="94" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>54</v>
@@ -4450,72 +4628,72 @@
         <v>31.37263244651167</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J94" s="2"/>
     </row>
-    <row r="95" spans="1:10" ht="45">
+    <row r="95" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H95" s="2">
-        <v>48.596354262354943</v>
+        <v>48.59635426235494</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="45">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="96" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H96" s="2">
         <v>29.5487379012331</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -4527,9 +4705,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -4540,12 +4718,12 @@
     <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16">
+    <row r="1" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4554,12 +4732,12 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="15">
+    <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4568,12 +4746,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4582,9 +4760,9 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15">
+    <row r="4" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>198</v>
       </c>
       <c r="B4" s="2">
         <v>334</v>
@@ -4596,9 +4774,9 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="15">
+    <row r="5" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B5" s="2">
         <v>17</v>
@@ -4610,9 +4788,9 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="15">
+    <row r="6" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
@@ -4624,9 +4802,9 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="15">
+    <row r="7" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B7" s="2">
         <v>171</v>
@@ -4638,9 +4816,9 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" ht="15">
+    <row r="8" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B8" s="2">
         <v>72</v>
@@ -4652,12 +4830,12 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" ht="15">
+    <row r="9" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -4666,12 +4844,12 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="15">
+    <row r="10" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -4680,7 +4858,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4690,7 +4868,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -4700,41 +4878,41 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" ht="16">
-      <c r="A13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G13" s="3" t="s">
+    <row r="13" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="C13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="30">
+      <c r="E13" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B14" s="2">
         <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
@@ -4743,24 +4921,24 @@
         <v>54</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="30">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B15" s="2">
         <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>25</v>
@@ -4769,65 +4947,65 @@
         <v>54</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2">
         <v>27</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="30">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B17" s="2">
         <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
